--- a/data/modelamiento/robustez_resultados_finales.xlsx
+++ b/data/modelamiento/robustez_resultados_finales.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Variables con prioridad_tesis == 'prioritaria': x_gcfid_guaiacol_ppm, x_gcfid_p_cresol_ppm, x_gcfid_o_cresol_ppm, x_gcfid_ethyl_octanoate_ppm, x_gcfid_4_ethyl_guaiacol_ppm (script 18, hoja 05_variables_finales_tesis).</t>
+          <t>Variables con prioridad_tesis == 'prioritaria': x_gcfid_4_ethyl_guaiacol_ppm, x_gcfid_o_cresol_ppm, x_gcfid_guaiacol_ppm, x_gcfid_p_cresol_ppm (script 18, hoja 05_variables_finales_tesis).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1319,7 +1319,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1400,15 +1400,25 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>importancia_norm_minmax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>score_combinado</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>estabilidad_consenso</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>prioridad_tesis</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ranking_consenso</t>
         </is>
@@ -1427,12 +1437,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>x_gcfid_guaiacol_ppm</t>
+          <t>x_gcfid_4_ethyl_guaiacol_ppm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gcfid guaiacol ppm</t>
+          <t>gcfid 4 ethyl guaiacol ppm</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1459,36 +1469,42 @@
         </is>
       </c>
       <c r="J2">
-        <v>0.9225</v>
+        <v>0.7275</v>
       </c>
       <c r="K2">
         <v>0.99</v>
       </c>
       <c r="L2">
-        <v>17.53402248779114</v>
+        <v>37.00629480951667</v>
       </c>
       <c r="M2">
-        <v>32.32363828864813</v>
+        <v>55.05258287798129</v>
       </c>
       <c r="N2">
-        <v>369</v>
+        <v>291</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>0.86375</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>1</v>
       </c>
     </row>
@@ -1505,12 +1521,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>x_gcfid_p_cresol_ppm</t>
+          <t>x_gcfid_o_cresol_ppm</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>gcfid p cresol ppm</t>
+          <t>gcfid o cresol ppm</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1537,36 +1553,42 @@
         </is>
       </c>
       <c r="J3">
-        <v>0.845</v>
+        <v>0.775</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>15.64268494518121</v>
+        <v>24.7345254209672</v>
       </c>
       <c r="M3">
-        <v>20.46041263495372</v>
+        <v>42.04518748284477</v>
       </c>
       <c r="N3">
-        <v>338</v>
+        <v>310</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3">
+        <v>0.649892437001329</v>
+      </c>
+      <c r="Q3">
+        <v>0.7124462185006646</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>2</v>
       </c>
     </row>
@@ -1583,12 +1605,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>x_gcfid_o_cresol_ppm</t>
+          <t>x_gcfid_guaiacol_ppm</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>gcfid o cresol ppm</t>
+          <t>gcfid guaiacol ppm</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1615,36 +1637,42 @@
         </is>
       </c>
       <c r="J4">
-        <v>0.775</v>
+        <v>0.9225</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L4">
-        <v>24.7345254209672</v>
+        <v>17.53402248779114</v>
       </c>
       <c r="M4">
-        <v>42.04518748284477</v>
+        <v>32.32363828864813</v>
       </c>
       <c r="N4">
-        <v>310</v>
+        <v>369</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4">
+        <v>0.4444656191985679</v>
+      </c>
+      <c r="Q4">
+        <v>0.683482809599284</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>3</v>
       </c>
     </row>
@@ -1661,12 +1689,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_octanoate_ppm</t>
+          <t>x_gcfid_p_cresol_ppm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>gcfid ethyl octanoate ppm</t>
+          <t>gcfid p cresol ppm</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1676,12 +1704,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>media_contextual</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H5">
@@ -1693,115 +1721,43 @@
         </is>
       </c>
       <c r="J5">
-        <v>0.7375</v>
+        <v>0.845</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5">
-        <v>2.319313847251581</v>
+        <v>15.64268494518121</v>
       </c>
       <c r="M5">
-        <v>9.17233425056237</v>
+        <v>20.46041263495372</v>
       </c>
       <c r="N5">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P5">
+        <v>0.3905066865552512</v>
+      </c>
+      <c r="Q5">
+        <v>0.6177533432776255</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R5">
+      <c r="T5">
         <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>M_pura</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>y_fenolico_comun</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>x_gcfid_4_ethyl_guaiacol_ppm</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>gcfid 4 ethyl guaiacol ppm</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>GC-FID</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>fenoles_volatiles</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>alta_directa</t>
-        </is>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>elastic_net; lasso; random_forest_restringido; ridge</t>
-        </is>
-      </c>
-      <c r="J6">
-        <v>0.7275</v>
-      </c>
-      <c r="K6">
-        <v>0.99</v>
-      </c>
-      <c r="L6">
-        <v>37.00629480951667</v>
-      </c>
-      <c r="M6">
-        <v>55.05258287798129</v>
-      </c>
-      <c r="N6">
-        <v>291</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="R6">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/modelamiento/robustez_resultados_finales.xlsx
+++ b/data/modelamiento/robustez_resultados_finales.xlsx
@@ -415,7 +415,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>0.396</t>
         </is>
       </c>
     </row>
@@ -427,7 +427,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.247</t>
         </is>
       </c>
     </row>
@@ -439,7 +439,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>0.196</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.2708</t>
+          <t>0.4208</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>6.3%</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-0.1329</t>
+          <t>-0.5626</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-0.3293</t>
+          <t>-0.5626</t>
         </is>
       </c>
     </row>
@@ -550,12 +550,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>random_forest_restringido sobre y_fenolico_comun en M_pura es el resultado predictivo principal de la tesis.</t>
+          <t>random_forest_restringido sobre y_fenolico_comun en M_pura es el resultado predictivo principal de la tesis, con una senal moderada y condicionada por el contraste comercial-experimental de la matriz (ver analisis de sensibilidad de muestras comerciales).</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MAE bootstrap = 0.271; R2 bootstrap = 0.3; Spearman bootstrap = 0.553 (n=100 iteraciones bootstrap agrupado).</t>
+          <t>MAE bootstrap = 0.396; R2 bootstrap = 0.247; Spearman bootstrap = 0.196 (n=100 iteraciones bootstrap agrupado por identificador_quimico, 10 grupos).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -572,12 +572,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>El resultado principal (y_fenolico_comun) es robusto a las unidades quimicamente atipicas detectadas en el EDA.</t>
+          <t>El desempeno de random_forest_restringido sobre y_fenolico_comun se mantiene en un rango similar al excluir las unidades quimicamente atipicas detectadas en el EDA, es decir, el resultado no se explica unicamente por esas unidades.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MAE bootstrap completo = 0.275 vs. sin unidades marcadas por T2/Q = 0.271 (diferencia = -1.4%).</t>
+          <t>MAE bootstrap completo = 0.396 vs. sin unidades marcadas por T2/Q = 0.421 (diferencia = 6.3%).</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -594,12 +594,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Las unidades marcadas como atipicas en el EDA no predicen sistematicamente peor con el modelo principal.</t>
+          <t>Las unidades marcadas como atipicas en el EDA no predicen sistematicamente peor con random_forest_restringido.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Residuo absoluto medio en unidades marcadas por el EDA = 0.188 vs. no marcadas = 0.261.</t>
+          <t>Residuo absoluto medio en unidades marcadas por el EDA = 0.46 vs. no marcadas = 0.414.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grados de libertad aproximados = -5 en M_pura (n_filas_modelables - n_predictores_usables, ver script 13); R2 bootstrap del modelo principal para y_frutal_comun es negativo (peor que predecir la media).</t>
+          <t>Grados de libertad aproximados = 0 en M_pura (n_filas_modelables - n_predictores_usables, ver script 13); R2 bootstrap del modelo principal para y_frutal_comun es negativo (peor que predecir la media).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Variables con prioridad_tesis == 'prioritaria': x_gcfid_4_ethyl_guaiacol_ppm, x_gcfid_o_cresol_ppm, x_gcfid_guaiacol_ppm, x_gcfid_p_cresol_ppm (script 18, hoja 05_variables_finales_tesis).</t>
+          <t>Variables con prioridad_tesis == 'prioritaria': x_gcfid_o_cresol_ppm, x_gcfid_p_cresol_ppm, x_gcfid_guaiacol_ppm (script 18, hoja 05_variables_finales_tesis).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -686,7 +686,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -747,10 +747,15 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>r2_agregado</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>spearman_media</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>bias_media</t>
         </is>
@@ -776,31 +781,34 @@
         <v>100</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0.274699676510561</v>
+        <v>0.3958918079843521</v>
       </c>
       <c r="G2">
-        <v>0.1738739844524413</v>
+        <v>0.1815655357116163</v>
       </c>
       <c r="H2">
-        <v>0.2782505398995955</v>
+        <v>0.3676043542027075</v>
       </c>
       <c r="I2">
-        <v>0.3873386261998266</v>
+        <v>0.6724121662057668</v>
       </c>
       <c r="J2">
-        <v>0.3565861569502497</v>
+        <v>0.4584316988326317</v>
       </c>
       <c r="K2">
-        <v>0.4140521389104801</v>
+        <v>0.03366392976372895</v>
       </c>
       <c r="L2">
-        <v>0.5971615371809208</v>
+        <v>0.2472767774976532</v>
       </c>
       <c r="M2">
-        <v>-0.01584230748942596</v>
+        <v>0.1964191152779068</v>
+      </c>
+      <c r="N2">
+        <v>0.0979813748934462</v>
       </c>
     </row>
     <row r="3">
@@ -823,31 +831,34 @@
         <v>100</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0.2708032005657093</v>
+        <v>0.4208030587638699</v>
       </c>
       <c r="G3">
-        <v>0.1851389647173243</v>
+        <v>0.1879150459080933</v>
       </c>
       <c r="H3">
-        <v>0.2751198383306488</v>
+        <v>0.3772324548251037</v>
       </c>
       <c r="I3">
-        <v>0.3670529579718041</v>
+        <v>0.8094813641602948</v>
       </c>
       <c r="J3">
-        <v>0.3622975150854907</v>
+        <v>0.4792064839475932</v>
       </c>
       <c r="K3">
-        <v>0.3615784113814984</v>
+        <v>-0.008538622902261093</v>
       </c>
       <c r="L3">
-        <v>0.5925368789645654</v>
+        <v>0.1986525416818175</v>
       </c>
       <c r="M3">
-        <v>-0.02632384062955291</v>
+        <v>0.2326573696451022</v>
+      </c>
+      <c r="N3">
+        <v>0.08877503805220822</v>
       </c>
     </row>
     <row r="4">
@@ -867,34 +878,37 @@
         </is>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>0.1630743069845821</v>
+        <v>0.3268152081672336</v>
       </c>
       <c r="G4">
-        <v>0.06423204168671023</v>
+        <v>0.1041772817460346</v>
       </c>
       <c r="H4">
-        <v>0.1531303571428616</v>
+        <v>0.2987839506172762</v>
       </c>
       <c r="I4">
-        <v>0.285966110543268</v>
+        <v>0.5375600396825431</v>
       </c>
       <c r="J4">
-        <v>0.2067445645319708</v>
+        <v>0.3570631684404933</v>
       </c>
       <c r="K4">
-        <v>-0.1328517511499179</v>
+        <v>-0.562630562477361</v>
       </c>
       <c r="L4">
-        <v>0.5298990900860094</v>
+        <v>-0.06044182733028913</v>
       </c>
       <c r="M4">
-        <v>0.05805111371195432</v>
+        <v>-0.04741690471746197</v>
+      </c>
+      <c r="N4">
+        <v>0.1053355708558768</v>
       </c>
     </row>
     <row r="5">
@@ -914,34 +928,37 @@
         </is>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>0.1666197762434753</v>
+        <v>0.3268152081672336</v>
       </c>
       <c r="G5">
-        <v>0.04690113609642446</v>
+        <v>0.1041772817460346</v>
       </c>
       <c r="H5">
-        <v>0.1653133994709018</v>
+        <v>0.2987839506172762</v>
       </c>
       <c r="I5">
-        <v>0.2966251675484979</v>
+        <v>0.5375600396825431</v>
       </c>
       <c r="J5">
-        <v>0.2164720903479702</v>
+        <v>0.3570631684404933</v>
       </c>
       <c r="K5">
-        <v>-0.3292504141086098</v>
+        <v>-0.562630562477361</v>
       </c>
       <c r="L5">
-        <v>0.4314388428625768</v>
+        <v>-0.06044182733028913</v>
       </c>
       <c r="M5">
-        <v>-0.009904915746214306</v>
+        <v>-0.04741690471746197</v>
+      </c>
+      <c r="N5">
+        <v>0.1053355708558768</v>
       </c>
     </row>
     <row r="6">
@@ -964,31 +981,34 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>0.2594539606622538</v>
+        <v>0.4360456476375756</v>
       </c>
       <c r="G6">
-        <v>0.1573722750677219</v>
+        <v>0.1807816117516983</v>
       </c>
       <c r="H6">
-        <v>0.2539683510006008</v>
+        <v>0.3915526893453431</v>
       </c>
       <c r="I6">
-        <v>0.3823481122427795</v>
+        <v>0.8397778280297081</v>
       </c>
       <c r="J6">
-        <v>0.3550912014041904</v>
+        <v>0.5140876532000473</v>
       </c>
       <c r="K6">
-        <v>0.2869068594104216</v>
+        <v>-0.5122353752554718</v>
       </c>
       <c r="L6">
-        <v>0.6283030083458696</v>
+        <v>-0.1401207208224828</v>
       </c>
       <c r="M6">
-        <v>0.03211539366024992</v>
+        <v>0.2162868776737471</v>
+      </c>
+      <c r="N6">
+        <v>0.0510777567313357</v>
       </c>
     </row>
     <row r="7">
@@ -1011,31 +1031,34 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0.2609777879296922</v>
+        <v>0.5609756360983928</v>
       </c>
       <c r="G7">
-        <v>0.156123489550167</v>
+        <v>0.1762062663793912</v>
       </c>
       <c r="H7">
-        <v>0.253403956162628</v>
+        <v>0.5457201058520949</v>
       </c>
       <c r="I7">
-        <v>0.3873083209305409</v>
+        <v>1.211899359095102</v>
       </c>
       <c r="J7">
-        <v>0.3517569020377483</v>
+        <v>0.6457457140931521</v>
       </c>
       <c r="K7">
-        <v>0.3043813523590186</v>
+        <v>-1.905240490713872</v>
       </c>
       <c r="L7">
-        <v>0.6299918253389589</v>
+        <v>-0.8243634072546819</v>
       </c>
       <c r="M7">
-        <v>0.009246692447588915</v>
+        <v>0.1255327039456431</v>
+      </c>
+      <c r="N7">
+        <v>-0.02987834697493302</v>
       </c>
     </row>
     <row r="8">
@@ -1055,34 +1078,37 @@
         </is>
       </c>
       <c r="D8">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F8">
-        <v>0.2179235109846491</v>
+        <v>0.3866299210810501</v>
       </c>
       <c r="G8">
-        <v>0.1049252006226224</v>
+        <v>0.1418590213962067</v>
       </c>
       <c r="H8">
-        <v>0.2158146729777669</v>
+        <v>0.4066025534315264</v>
       </c>
       <c r="I8">
-        <v>0.3797200141402716</v>
+        <v>0.5923895251353619</v>
       </c>
       <c r="J8">
-        <v>0.2732786114833946</v>
+        <v>0.4188874186893458</v>
       </c>
       <c r="K8">
-        <v>-1.014268951096798</v>
+        <v>-3.886854539367101</v>
       </c>
       <c r="L8">
-        <v>0.352651157153305</v>
+        <v>-0.5256405080022972</v>
       </c>
       <c r="M8">
-        <v>0.06486296948120239</v>
+        <v>-0.4752765720618853</v>
+      </c>
+      <c r="N8">
+        <v>0.08894803386116489</v>
       </c>
     </row>
     <row r="9">
@@ -1102,34 +1128,37 @@
         </is>
       </c>
       <c r="D9">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F9">
-        <v>0.2388778232432364</v>
+        <v>0.3866299210810501</v>
       </c>
       <c r="G9">
-        <v>0.1342855532606997</v>
+        <v>0.1418590213962067</v>
       </c>
       <c r="H9">
-        <v>0.2201142362501491</v>
+        <v>0.4066025534315264</v>
       </c>
       <c r="I9">
-        <v>0.3944809972003201</v>
+        <v>0.5923895251353619</v>
       </c>
       <c r="J9">
-        <v>0.3010012634586377</v>
+        <v>0.4188874186893458</v>
       </c>
       <c r="K9">
-        <v>-1.03148486595352</v>
+        <v>-3.886854539367101</v>
       </c>
       <c r="L9">
-        <v>0.2850201148449314</v>
+        <v>-0.5256405080022972</v>
       </c>
       <c r="M9">
-        <v>0.06780660487439319</v>
+        <v>-0.4752765720618853</v>
+      </c>
+      <c r="N9">
+        <v>0.08894803386116489</v>
       </c>
     </row>
   </sheetData>
@@ -1202,14 +1231,14 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>alerta_gl_ajustado</t>
+          <t>aceptable_para_small_data</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -1234,10 +1263,10 @@
         <v>34</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1266,10 +1295,10 @@
         <v>13</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1298,14 +1327,14 @@
         <v>30</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>alerta_gl_ajustado</t>
+          <t>aceptable_para_small_data</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -1319,7 +1348,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1437,12 +1466,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>x_gcfid_4_ethyl_guaiacol_ppm</t>
+          <t>x_gcfid_o_cresol_ppm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gcfid 4 ethyl guaiacol ppm</t>
+          <t>gcfid o cresol ppm</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1469,19 +1498,19 @@
         </is>
       </c>
       <c r="J2">
-        <v>0.7275</v>
+        <v>0.715</v>
       </c>
       <c r="K2">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="L2">
-        <v>37.00629480951667</v>
+        <v>28.44075983429025</v>
       </c>
       <c r="M2">
-        <v>55.05258287798129</v>
+        <v>44.11258233780747</v>
       </c>
       <c r="N2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -1489,10 +1518,10 @@
         </is>
       </c>
       <c r="P2">
-        <v>1</v>
+        <v>0.7530590235807832</v>
       </c>
       <c r="Q2">
-        <v>0.86375</v>
+        <v>0.7340295117903917</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -1521,12 +1550,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>x_gcfid_o_cresol_ppm</t>
+          <t>x_gcfid_p_cresol_ppm</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>gcfid o cresol ppm</t>
+          <t>gcfid p cresol ppm</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1553,19 +1582,19 @@
         </is>
       </c>
       <c r="J3">
-        <v>0.775</v>
+        <v>0.8225</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>24.7345254209672</v>
+        <v>18.55959607002194</v>
       </c>
       <c r="M3">
-        <v>42.04518748284477</v>
+        <v>26.97510061119657</v>
       </c>
       <c r="N3">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -1573,10 +1602,10 @@
         </is>
       </c>
       <c r="P3">
-        <v>0.649892437001329</v>
+        <v>0.4615626259327242</v>
       </c>
       <c r="Q3">
-        <v>0.7124462185006646</v>
+        <v>0.6420313129663622</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -1637,19 +1666,19 @@
         </is>
       </c>
       <c r="J4">
-        <v>0.9225</v>
+        <v>0.7725</v>
       </c>
       <c r="K4">
-        <v>0.99</v>
+        <v>0.88</v>
       </c>
       <c r="L4">
-        <v>17.53402248779114</v>
+        <v>18.91201360039875</v>
       </c>
       <c r="M4">
-        <v>32.32363828864813</v>
+        <v>37.06607755418248</v>
       </c>
       <c r="N4">
-        <v>369</v>
+        <v>309</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1657,10 +1686,10 @@
         </is>
       </c>
       <c r="P4">
-        <v>0.4444656191985679</v>
+        <v>0.471959016785424</v>
       </c>
       <c r="Q4">
-        <v>0.683482809599284</v>
+        <v>0.622229508392712</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1674,90 +1703,6 @@
       </c>
       <c r="T4">
         <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>M_pura</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>y_fenolico_comun</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>x_gcfid_p_cresol_ppm</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>gcfid p cresol ppm</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>GC-FID</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>fenoles_volatiles</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>alta_directa</t>
-        </is>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>elastic_net; lasso; random_forest_restringido; ridge</t>
-        </is>
-      </c>
-      <c r="J5">
-        <v>0.845</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>15.64268494518121</v>
-      </c>
-      <c r="M5">
-        <v>20.46041263495372</v>
-      </c>
-      <c r="N5">
-        <v>338</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P5">
-        <v>0.3905066865552512</v>
-      </c>
-      <c r="Q5">
-        <v>0.6177533432776255</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="T5">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
